--- a/ui_runner/graded_slate/2026-04-02/graded_nba1q_2026-04-02.xlsx
+++ b/ui_runner/graded_slate/2026-04-02/graded_nba1q_2026-04-02.xlsx
@@ -705,7 +705,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NBA SLATE GRADE  |  2026-04-02  |  Generated 2026-04-03 15:43</t>
+          <t>NBA SLATE GRADE  |  2026-04-02  |  Generated 2026-04-03 19:03</t>
         </is>
       </c>
     </row>
@@ -31203,7 +31203,7 @@
         <v>0.626</v>
       </c>
       <c r="T299" s="4" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="U299" s="33" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         <v>0.6256</v>
       </c>
       <c r="T301" s="4" t="n">
-        <v/>
+        <v>2</v>
       </c>
       <c r="U301" s="33" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>0.6256</v>
       </c>
       <c r="T302" s="13" t="n">
-        <v/>
+        <v>4</v>
       </c>
       <c r="U302" s="33" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>0.6256</v>
       </c>
       <c r="T303" s="4" t="n">
-        <v/>
+        <v>3</v>
       </c>
       <c r="U303" s="33" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>0.6238</v>
       </c>
       <c r="T306" s="13" t="n">
-        <v/>
+        <v>2</v>
       </c>
       <c r="U306" s="33" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>0.6235000000000001</v>
       </c>
       <c r="T309" s="4" t="n">
-        <v/>
+        <v>2</v>
       </c>
       <c r="U309" s="33" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>0.6235000000000001</v>
       </c>
       <c r="T310" s="13" t="n">
-        <v/>
+        <v>3</v>
       </c>
       <c r="U310" s="33" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>0.6235000000000001</v>
       </c>
       <c r="T311" s="4" t="n">
-        <v/>
+        <v>4</v>
       </c>
       <c r="U311" s="33" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>0.6233</v>
       </c>
       <c r="T312" s="13" t="n">
-        <v/>
+        <v>4</v>
       </c>
       <c r="U312" s="33" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>0.6208</v>
       </c>
       <c r="T315" s="4" t="n">
-        <v/>
+        <v>5</v>
       </c>
       <c r="U315" s="33" t="inlineStr">
         <is>
@@ -32818,7 +32818,7 @@
         <v>0.6205000000000001</v>
       </c>
       <c r="T316" s="13" t="n">
-        <v/>
+        <v>5</v>
       </c>
       <c r="U316" s="33" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>0.6199</v>
       </c>
       <c r="T318" s="13" t="n">
-        <v/>
+        <v>3</v>
       </c>
       <c r="U318" s="33" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>0.6199</v>
       </c>
       <c r="T319" s="4" t="n">
-        <v/>
+        <v>2</v>
       </c>
       <c r="U319" s="33" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>0.6199</v>
       </c>
       <c r="T320" s="13" t="n">
-        <v/>
+        <v>3</v>
       </c>
       <c r="U320" s="33" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>0.6198</v>
       </c>
       <c r="T321" s="4" t="n">
-        <v/>
+        <v>2</v>
       </c>
       <c r="U321" s="33" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>0.6198</v>
       </c>
       <c r="T324" s="13" t="n">
-        <v/>
+        <v>3</v>
       </c>
       <c r="U324" s="33" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>0.6198</v>
       </c>
       <c r="T325" s="4" t="n">
-        <v/>
+        <v>2</v>
       </c>
       <c r="U325" s="33" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>0.6198</v>
       </c>
       <c r="T326" s="13" t="n">
-        <v/>
+        <v>3</v>
       </c>
       <c r="U326" s="33" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>0.6198</v>
       </c>
       <c r="T327" s="4" t="n">
-        <v/>
+        <v>4</v>
       </c>
       <c r="U327" s="33" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>0.6196</v>
       </c>
       <c r="T329" s="4" t="n">
-        <v/>
+        <v>5</v>
       </c>
       <c r="U329" s="33" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>0.6192</v>
       </c>
       <c r="T330" s="13" t="n">
-        <v/>
+        <v>5</v>
       </c>
       <c r="U330" s="33" t="inlineStr">
         <is>
@@ -34243,7 +34243,7 @@
         <v>0.6185</v>
       </c>
       <c r="T331" s="4" t="n">
-        <v/>
+        <v>5</v>
       </c>
       <c r="U331" s="33" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>0.6183999999999999</v>
       </c>
       <c r="T332" s="13" t="n">
-        <v/>
+        <v>4</v>
       </c>
       <c r="U332" s="33" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>0.6172</v>
       </c>
       <c r="T333" s="4" t="n">
-        <v/>
+        <v>4</v>
       </c>
       <c r="U333" s="33" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>0.6169</v>
       </c>
       <c r="T335" s="4" t="n">
-        <v/>
+        <v>4</v>
       </c>
       <c r="U335" s="33" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>0.616</v>
       </c>
       <c r="T337" s="4" t="n">
-        <v/>
+        <v>5</v>
       </c>
       <c r="U337" s="33" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>0.6145</v>
       </c>
       <c r="T338" s="13" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="U338" s="33" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>0.6112</v>
       </c>
       <c r="T340" s="13" t="n">
-        <v/>
+        <v>2</v>
       </c>
       <c r="U340" s="33" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>0.6112</v>
       </c>
       <c r="T341" s="4" t="n">
-        <v/>
+        <v>2</v>
       </c>
       <c r="U341" s="33" t="inlineStr">
         <is>
